--- a/web/public/forms/dongbari-haeche.xlsx
+++ b/web/public/forms/dongbari-haeche.xlsx
@@ -907,7 +907,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="81" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="81" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="81" t="inlineStr">
@@ -3875,7 +3875,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6412,7 +6412,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="81" t="inlineStr">
@@ -8153,7 +8153,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="81" t="inlineStr">
@@ -9232,7 +9232,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="81" t="inlineStr">

--- a/web/public/forms/dongbari-haeche.xlsx
+++ b/web/public/forms/dongbari-haeche.xlsx
@@ -892,7 +892,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
